--- a/Data/05_VehicleElectricMotorsWeight.xlsx
+++ b/Data/05_VehicleElectricMotorsWeight.xlsx
@@ -2766,7 +2766,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2788,7 +2787,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
@@ -2810,7 +2808,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
@@ -2825,7 +2822,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
@@ -2840,7 +2836,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
@@ -2876,7 +2871,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
@@ -3001,13 +2995,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="C29" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="D29" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="E29" t="n">
         <v>20</v>
@@ -3020,7 +3014,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>near-saturated; &gt;62% already hands-free capable</t>
+          <t>near-saturated on EUROPEAN content; raised 2026-08-12 for Chinese executive-interior adjustment axes -- see AUX_MOTOR_ADOPTION_RESEARCH.md 8.6</t>
         </is>
       </c>
     </row>
